--- a/AMZN.xlsx
+++ b/AMZN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8239B6E1-0319-764A-8017-B1E643287080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D51AA87-E754-2247-AF6E-B093A3C2600F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="443">
   <si>
     <t>Ticker</t>
   </si>
@@ -1469,6 +1469,18 @@
   </si>
   <si>
     <t>Fulfillment COGS</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2430,6 +2442,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="20" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2443,12 +2461,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2469,14 +2481,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15298,11 +15310,11 @@
     <v>Powered by Refinitiv</v>
     <v>287.2</v>
     <v>196</v>
-    <v>1.4914000000000001</v>
-    <v>1.0900000000000001</v>
-    <v>4.3949999999999996E-3</v>
-    <v>-4.2500000000000003E-2</v>
-    <v>-1.706E-4</v>
+    <v>1.4919</v>
+    <v>4.01</v>
+    <v>1.6099000000000002E-2</v>
+    <v>0.69</v>
+    <v>2.7260000000000001E-3</v>
     <v>USD</v>
     <v>Amazon.com, Inc. offers a variety of products and services to customers. The products offered through its stores include merchandise and content it has purchased for resale and products offered by third-party sellers. The Company's segments include North America, International, and Amazon Web Services (AWS). It serves consumers through its online and physical stores and focuses on selection, price, and convenience. Customers access its offerings through its websites, mobile apps, Alexa, devices, streaming, and physically visiting its stores. It also manufactures and sells electronic devices, including Kindle, Fire tablet, Fire TV, Echo, Ring, Blink, and eero, and develops and produces media content. It serves developers and enterprises of all sizes, including start-ups, government agencies, and academic institutions, through AWS, which offers a set of on-demand technology services, including compute, storage, database, analytics, and machine learning, and other services.</v>
     <v>1595000</v>
@@ -15310,25 +15322,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>410 Terry Avenue North, SEATTLE, WA, 98109 US</v>
-    <v>250.79</v>
+    <v>254.68</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46321.853396747654</v>
+    <v>46322.925002128904</v>
     <v>0</v>
-    <v>247.23</v>
-    <v>2686761957900</v>
+    <v>248.71010000000001</v>
+    <v>2730015061000</v>
     <v>AMAZON.COM, INC.</v>
     <v>AMAZON.COM, INC.</v>
-    <v>249.47</v>
-    <v>20.0352</v>
-    <v>248</v>
+    <v>250.42500000000001</v>
+    <v>20.357800000000001</v>
     <v>249.09</v>
-    <v>249.04750000000001</v>
+    <v>253.1</v>
+    <v>253.79</v>
     <v>10786310000</v>
     <v>AMZN</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>31596550</v>
-    <v>36513473</v>
+    <v>34408567</v>
+    <v>36102152</v>
     <v>1996</v>
   </rv>
   <rv s="2">
@@ -15352,17 +15364,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.55</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
+    <v>50.03</v>
     <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -16188,7 +16200,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>2720062.8</v>
+        <v>2763852</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16196,7 +16208,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>63.427359384302612</v>
+        <v>63.383270030357082</v>
       </c>
       <c r="K3" s="236" t="s">
         <v>387</v>
@@ -16215,7 +16227,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>2725968.8</v>
+        <v>2769758</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16223,7 +16235,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>286.72485233641686</v>
+        <v>286.65973807541792</v>
       </c>
       <c r="K4" s="236" t="s">
         <v>388</v>
@@ -16235,7 +16247,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -16250,7 +16262,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>265.3477196202486</v>
+        <v>265.34475019767859</v>
       </c>
       <c r="K5" s="236" t="s">
         <v>389</v>
@@ -16262,14 +16274,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>249.04750000000001</v>
+        <v>253.79</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>42.66893793975332</v>
+        <v>43.355848057134224</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16277,7 +16289,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>180.57660521715539</v>
+        <v>180.53559494386667</v>
       </c>
       <c r="K6" s="237" t="s">
         <v>390</v>
@@ -16289,14 +16301,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.0900000000000001</v>
+        <v>4.01</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>3.4910267926206688</v>
+        <v>3.5472274327042079</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16304,7 +16316,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>267.40521414570168</v>
+        <v>267.34448695970542</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -16313,14 +16325,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-4.2500000000000003E-2</v>
+        <v>0.69</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>-1.1374369738816325E-2</v>
+        <v>-1.1194159455716153E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16328,7 +16340,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>212.69635014076502</v>
+        <v>212.65356804140515</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16337,14 +16349,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.3949999999999996E-3</v>
+        <v>1.6099000000000002E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>2.3436252418842868E-2</v>
+        <v>2.3064939213787321E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16352,7 +16364,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.14610642683060332</v>
+        <v>-0.15980415629630521</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -16361,7 +16373,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.706E-4</v>
+        <v>2.7260000000000001E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
@@ -16416,7 +16428,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4914000000000001</v>
+        <v>1.4919</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -16439,7 +16451,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>36513473</v>
+        <v>36102152</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -16453,7 +16465,7 @@
       </c>
       <c r="I14" s="239">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>-25.932606967926382</v>
+        <v>-25.918838126809213</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -16462,7 +16474,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>-2.1712733985406515E-3</v>
+        <v>-2.1368727413768897E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16495,7 +16507,7 @@
       </c>
       <c r="I17" s="234">
         <f ca="1">DCF!C15</f>
-        <v>0.11380869534434501</v>
+        <v>0.11385928664528444</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16517,7 +16529,7 @@
       </c>
       <c r="I18" s="235">
         <f ca="1">Multiples!C54</f>
-        <v>0.11699300000000001</v>
+        <v>0.1169955</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16590,7 +16602,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16605,7 +16617,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22330,12 +22342,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -22343,6 +22349,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -23402,16 +23414,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23533,7 +23545,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23542,7 +23554,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>2720062.8</v>
+        <v>2763852</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23560,7 +23572,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23569,7 +23581,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4914000000000001</v>
+        <v>1.4919</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23612,7 +23624,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>4.5242525263984347E-2</v>
+        <v>4.4557662511675755E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23621,7 +23633,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.95475747473601569</v>
+        <v>0.95544233748832419</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23639,7 +23651,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11699300000000001</v>
+        <v>0.1169955</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23648,7 +23660,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11380869534434501</v>
+        <v>0.11385928664528444</v>
       </c>
     </row>
   </sheetData>
@@ -23899,7 +23911,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>1030994.967544832</v>
+        <v>1030439.2486752947</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23953,23 +23965,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-11463.989431555377</v>
+        <v>-11463.468739088876</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-1389.0143510590401</v>
+        <v>-1388.8881763294055</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>23691.846680030721</v>
+        <v>23688.618587613317</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>30922.937580426282</v>
+        <v>30917.319904733416</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>55315.449956956989</v>
+        <v>55302.889006002733</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23988,7 +24000,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>601455.53404178494</v>
+        <v>600994.83814856817</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -24011,7 +24023,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11380869534434501</v>
+        <v>0.11385928664528444</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -24026,7 +24038,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>97077.230434799567</v>
+        <v>97056.470582931186</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -24035,7 +24047,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>601455.53404178494</v>
+        <v>600994.83814856817</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -24044,7 +24056,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>698532.7644765845</v>
+        <v>698051.30873149936</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -24071,7 +24083,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>692626.7644765845</v>
+        <v>692145.30873149936</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -24089,7 +24101,7 @@
       </c>
       <c r="C26" s="233">
         <f ca="1">C24/C25</f>
-        <v>63.427359384302612</v>
+        <v>63.383270030357082</v>
       </c>
     </row>
   </sheetData>
@@ -24358,23 +24370,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>-11463.989431555377</v>
+        <v>-11463.468739088876</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>-1389.0143510590401</v>
+        <v>-1388.8881763294055</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>23691.846680030721</v>
+        <v>23688.618587613317</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>30922.937580426282</v>
+        <v>30917.319904733416</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>55315.449956956989</v>
+        <v>55302.889006002733</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -25160,7 +25172,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11380869534434501</v>
+        <v>0.11385928664528444</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -25186,7 +25198,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>3095179.6070358292</v>
+        <v>3094476.7582066352</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -25195,7 +25207,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>3136941.387513672</v>
+        <v>3136230.3397835637</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -25222,7 +25234,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>3131035.387513672</v>
+        <v>3130324.3397835637</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -25240,7 +25252,7 @@
       </c>
       <c r="C50" s="233">
         <f ca="1">C48/C49</f>
-        <v>286.72485233641686</v>
+        <v>286.65973807541792</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -25264,7 +25276,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11699300000000001</v>
+        <v>0.1169955</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -25299,7 +25311,7 @@
       </c>
       <c r="C58" s="233">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>265.3477196202486</v>
+        <v>265.34475019767859</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -25323,7 +25335,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11380869534434501</v>
+        <v>0.11385928664528444</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25349,7 +25361,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>1936040.7484934945</v>
+        <v>1935601.1152100957</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25358,7 +25370,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>1977802.528971337</v>
+        <v>1977354.6967870241</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25385,7 +25397,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>1971896.5289713368</v>
+        <v>1971448.6967870239</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25403,7 +25415,7 @@
       </c>
       <c r="C71" s="233">
         <f ca="1">C69/C70</f>
-        <v>180.57660521715539</v>
+        <v>180.53559494386667</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -25427,7 +25439,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11380869534434501</v>
+        <v>0.11385928664528444</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25453,7 +25465,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>2884209.1579932193</v>
+        <v>2883554.2160230549</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25462,7 +25474,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>2925970.9384710621</v>
+        <v>2925307.7975999834</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25489,7 +25501,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>2920064.9384710621</v>
+        <v>2919401.7975999834</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25507,22 +25519,22 @@
       </c>
       <c r="C84" s="233">
         <f ca="1">C82/C83</f>
-        <v>267.40521414570168</v>
+        <v>267.34448695970542</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -25572,7 +25584,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>63.427359384302612</v>
+        <v>63.383270030357082</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25581,7 +25593,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>286.72485233641686</v>
+        <v>286.65973807541792</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25590,7 +25602,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>265.3477196202486</v>
+        <v>265.34475019767859</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -25599,7 +25611,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>180.57660521715539</v>
+        <v>180.53559494386667</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25608,7 +25620,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>267.40521414570168</v>
+        <v>267.34448695970542</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25617,7 +25629,7 @@
       </c>
       <c r="C10" s="233">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>212.69635014076502</v>
+        <v>212.65356804140515</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25626,7 +25638,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25635,7 +25647,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.14610642683060332</v>
+        <v>-0.15980415629630521</v>
       </c>
     </row>
   </sheetData>
@@ -26144,7 +26156,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11699300000000001</v>
+        <v>0.1169955</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -26398,7 +26410,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-304567.06455012952</v>
+        <v>-304402.89918546908</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26452,23 +26464,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-22344.279690425497</v>
+        <v>-22343.264817010469</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-20662.981154068893</v>
+        <v>-20661.104178457681</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>-19108.192167696401</v>
+        <v>-19105.588613356384</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>-17670.393502039042</v>
+        <v>-17667.183375581888</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>-16340.782203602161</v>
+        <v>-16337.071562832298</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26487,15 +26499,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-177676.47003822192</v>
+        <v>-177540.37548852549</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="266" t="s">
+      <c r="B14" s="265" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="267"/>
+      <c r="C14" s="266"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -26503,7 +26515,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26512,7 +26524,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-25.932606967926382</v>
+        <v>-25.918838126809213</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26522,20 +26534,20 @@
       <c r="C17" s="158">
         <v>0.03</v>
       </c>
-      <c r="E17" s="265" t="s">
+      <c r="E17" s="267" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="265"/>
-      <c r="G17" s="265"/>
-      <c r="H17" s="265"/>
-      <c r="I17" s="265"/>
+      <c r="F17" s="267"/>
+      <c r="G17" s="267"/>
+      <c r="H17" s="267"/>
+      <c r="I17" s="267"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="266" t="s">
+      <c r="B19" s="265" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="267"/>
+      <c r="C19" s="266"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -26551,7 +26563,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11380869534434501</v>
+        <v>0.11385928664528444</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26569,7 +26581,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>2686684.74</v>
+        <v>2729936.6</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26596,15 +26608,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>2692590.74</v>
+        <v>2735842.6</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="266" t="s">
+      <c r="B28" s="265" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="267"/>
+      <c r="C28" s="266"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -26612,7 +26624,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-96126.628717832005</v>
+        <v>-96114.212547238712</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26621,7 +26633,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>-177676.47003822192</v>
+        <v>-177540.37548852549</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26630,7 +26642,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>-273803.09875605395</v>
+        <v>-273654.58803576417</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26657,7 +26669,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>-279709.09875605395</v>
+        <v>-279560.58803576417</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26675,21 +26687,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>-25.932606967926382</v>
+        <v>-25.918838126809213</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33478,7 +33490,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33549,7 +33561,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34855,7 +34867,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>42.66893793975332</v>
+        <v>43.355848057134224</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34892,7 +34904,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>3.4910267926206688</v>
+        <v>3.5472274327042079</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34953,7 +34965,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>4.8705354048076579</v>
+        <v>4.948944200717885</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -35014,7 +35026,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>2720062.8</v>
+        <v>2763852</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -35075,7 +35087,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>2725968.8</v>
+        <v>2769758</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -35112,7 +35124,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>3.5142955858085805</v>
+        <v>3.5707482466996701</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -35149,7 +35161,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>29.088791190029024</v>
+        <v>29.556065391838825</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -35284,7 +35296,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="153">AC154/AC158</f>
-        <v>-87.916959177736828</v>
+        <v>-89.33229904004655</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -35321,7 +35333,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>-38.971914180195384</v>
+        <v>-39.597948104141771</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -35358,7 +35370,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="156">AC158/AC154</f>
-        <v>-1.1374369738816325E-2</v>
+        <v>-1.1194159455716153E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -35395,7 +35407,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>2.3436252418842868E-2</v>
+        <v>2.3064939213787321E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -36009,7 +36021,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>-2.1712733985406515E-3</v>
+        <v>-2.1368727413768897E-3</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -38019,7 +38031,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -38052,7 +38064,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -38068,7 +38080,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>2720062.8</v>
+        <v>2763852</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -38088,7 +38100,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>2725968.8</v>
+        <v>2769758</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -38108,7 +38120,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>42.66893793975332</v>
+        <v>43.355848057134224</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -38128,7 +38140,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>3.4910267926206688</v>
+        <v>3.5472274327042079</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -38148,7 +38160,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>4.8705354048076579</v>
+        <v>4.948944200717885</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -38168,7 +38180,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>3.5142955858085805</v>
+        <v>3.5707482466996701</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -38177,7 +38189,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>29.088791190029024</v>
+        <v>29.556065391838825</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -38413,7 +38425,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>2.3436252418842868E-2</v>
+        <v>2.3064939213787321E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -38429,7 +38441,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>-1.1374369738816325E-2</v>
+        <v>-1.1194159455716153E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -38514,7 +38526,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>-2.1712733985406515E-3</v>
+        <v>-2.1368727413768897E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38568,8 +38580,51 @@
         <v>2.300904255319149</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="251" t="s">
+        <v>439</v>
+      </c>
+      <c r="C57" s="251"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C58" s="172">
+        <f ca="1">Statement!AC160</f>
+        <v>-89.33229904004655</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C59" s="172">
+        <f ca="1">Statement!AC161</f>
+        <v>-39.597948104141771</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="C60" s="173">
+        <f>Statement!AC167</f>
+        <v>-9.0175082741880394E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="C61" s="173">
+        <f>Statement!AC168</f>
+        <v>-3.9886293316831682E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -38594,7 +38649,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I99"/>
+  <dimension ref="B1:I105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -38693,7 +38748,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>249.09</v>
+        <v>253.1</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38722,7 +38777,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>2720062.8</v>
+        <v>2763852</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38751,7 +38806,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>2725968.8</v>
+        <v>2769758</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38780,7 +38835,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>42.66893793975332</v>
+        <v>43.355848057134224</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38809,7 +38864,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>3.4910267926206688</v>
+        <v>3.5472274327042079</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38838,7 +38893,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>4.8705354048076579</v>
+        <v>4.948944200717885</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38867,7 +38922,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>3.5142955858085805</v>
+        <v>3.5707482466996701</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38896,7 +38951,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>29.088791190029024</v>
+        <v>29.556065391838825</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39669,7 +39724,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>2.3436252418842868E-2</v>
+        <v>2.3064939213787321E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39698,7 +39753,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>-1.1374369738816325E-2</v>
+        <v>-1.1194159455716153E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -40021,7 +40076,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>-2.1712733985406515E-3</v>
+        <v>-2.1368727413768897E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40358,269 +40413,396 @@
       </c>
       <c r="I85" s="195"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C88" s="172">
+        <f>Statement!M160</f>
+        <v>-62.822556489466216</v>
+      </c>
+      <c r="D88" s="172">
+        <f>Statement!N160</f>
+        <v>-23.570288930273318</v>
+      </c>
+      <c r="E88" s="172">
+        <f>Statement!O160</f>
+        <v>196.10903587991211</v>
+      </c>
+      <c r="F88" s="172">
+        <f>Statement!P160</f>
+        <v>218.96603846507776</v>
+      </c>
+      <c r="G88" s="172">
+        <f>Statement!Q160</f>
+        <v>-213.83986748216105</v>
+      </c>
+      <c r="I88" s="172">
+        <f ca="1">Statement!AC160</f>
+        <v>-89.33229904004655</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C89" s="172">
+        <f>Statement!M161</f>
+        <v>-65.014484835964183</v>
+      </c>
+      <c r="D89" s="172">
+        <f>Statement!N161</f>
+        <v>-28.251417232066395</v>
+      </c>
+      <c r="E89" s="172">
+        <f>Statement!O161</f>
+        <v>110.70130235043659</v>
+      </c>
+      <c r="F89" s="172">
+        <f>Statement!P161</f>
+        <v>171.57022952231122</v>
+      </c>
+      <c r="G89" s="172">
+        <f>Statement!Q161</f>
+        <v>-101.80875231754139</v>
+      </c>
+      <c r="I89" s="172">
+        <f ca="1">Statement!AC161</f>
+        <v>-39.597948104141771</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="C90" s="173">
+        <f>Statement!M167</f>
+        <v>-5.4975753298477266E-2</v>
+      </c>
+      <c r="D90" s="173">
+        <f>Statement!N167</f>
+        <v>-5.9071992653453517E-2</v>
+      </c>
+      <c r="E90" s="173">
+        <f>Statement!O167</f>
+        <v>2.4806932762113716E-2</v>
+      </c>
+      <c r="F90" s="173">
+        <f>Statement!P167</f>
+        <v>2.1295781775610305E-2</v>
+      </c>
+      <c r="G90" s="173">
+        <f>Statement!Q167</f>
+        <v>-3.3702849344556821E-2</v>
+      </c>
+      <c r="I90" s="173">
+        <f>Statement!AC167</f>
+        <v>-9.0175082741880394E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="C91" s="173">
+        <f>Statement!M168</f>
+        <v>-5.8496622124974994E-2</v>
+      </c>
+      <c r="D91" s="173">
+        <f>Statement!N168</f>
+        <v>-7.1041260119498115E-2</v>
+      </c>
+      <c r="E91" s="173">
+        <f>Statement!O168</f>
+        <v>1.4255765199161425E-2</v>
+      </c>
+      <c r="F91" s="173">
+        <f>Statement!P168</f>
+        <v>1.703401002258766E-2</v>
+      </c>
+      <c r="G91" s="173">
+        <f>Statement!Q168</f>
+        <v>-1.6420150531995022E-2</v>
+      </c>
+      <c r="I91" s="173">
+        <f>Statement!AC168</f>
+        <v>-3.9886293316831682E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="C94" s="173">
+        <f>Statement!M216</f>
+        <v>0</v>
+      </c>
+      <c r="D94" s="173">
+        <f>Statement!N216</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="173">
+        <f>Statement!O216</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="173">
+        <f>Statement!P216</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="173">
+        <f>Statement!Q216</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="195"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="str">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="str">
         <f>Statement!B202</f>
         <v>Online Stores</v>
       </c>
-      <c r="C89" s="173">
+      <c r="C98" s="173">
         <f>Statement!M202</f>
         <v>1</v>
       </c>
-      <c r="D89" s="173">
+      <c r="D98" s="173">
         <f>Statement!N202</f>
         <v>-9.3256782618484739E-3</v>
       </c>
-      <c r="E89" s="173">
+      <c r="E98" s="173">
         <f>Statement!O202</f>
         <v>5.394447373684115E-2</v>
       </c>
-      <c r="F89" s="173">
+      <c r="F98" s="173">
         <f>Statement!P202</f>
         <v>6.5367961634004962E-2</v>
       </c>
-      <c r="G89" s="173">
+      <c r="G98" s="173">
         <f>Statement!Q202</f>
         <v>9.0102781454808947E-2</v>
       </c>
-      <c r="I89" s="195"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="20" t="str">
+      <c r="I98" s="195"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="str">
         <f>Statement!B203</f>
         <v>Physical Stores</v>
       </c>
-      <c r="C90" s="173">
+      <c r="C99" s="173">
         <f>Statement!M203</f>
         <v>1</v>
       </c>
-      <c r="D90" s="173">
+      <c r="D99" s="173">
         <f>Statement!N203</f>
         <v>0.1105710102489019</v>
       </c>
-      <c r="E90" s="173">
+      <c r="E99" s="173">
         <f>Statement!O203</f>
         <v>5.626746822760112E-2</v>
       </c>
-      <c r="F90" s="173">
+      <c r="F99" s="173">
         <f>Statement!P203</f>
         <v>5.9161258112830753E-2</v>
       </c>
-      <c r="G90" s="173">
+      <c r="G99" s="173">
         <f>Statement!Q203</f>
         <v>6.3445675229790249E-2</v>
       </c>
-      <c r="I90" s="195"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="20" t="str">
+      <c r="I99" s="195"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="str">
         <f>Statement!B204</f>
         <v>Third party seller services</v>
       </c>
-      <c r="C91" s="173">
+      <c r="C100" s="173">
         <f>Statement!M204</f>
         <v>1</v>
       </c>
-      <c r="D91" s="173">
+      <c r="D100" s="173">
         <f>Statement!N204</f>
         <v>0.13882708047133488</v>
       </c>
-      <c r="E91" s="173">
+      <c r="E100" s="173">
         <f>Statement!O204</f>
         <v>0.18975330456352577</v>
       </c>
-      <c r="F91" s="173">
+      <c r="F100" s="173">
         <f>Statement!P204</f>
         <v>0.11490649968226314</v>
       </c>
-      <c r="G91" s="173">
+      <c r="G100" s="173">
         <f>Statement!Q204</f>
         <v>0.10257067103864333</v>
       </c>
-      <c r="I91" s="195"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B92" s="20" t="str">
+      <c r="I100" s="195"/>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B101" s="20" t="str">
         <f>Statement!B205</f>
         <v>Advertising services</v>
       </c>
-      <c r="C92" s="173">
+      <c r="C101" s="173">
         <f>Statement!M205</f>
         <v>1</v>
       </c>
-      <c r="D92" s="173">
+      <c r="D101" s="173">
         <f>Statement!N205</f>
         <v>0.21113607188703465</v>
       </c>
-      <c r="E92" s="173">
+      <c r="E101" s="173">
         <f>Statement!O205</f>
         <v>0.2429052174143459</v>
       </c>
-      <c r="F92" s="173">
+      <c r="F101" s="173">
         <f>Statement!P205</f>
         <v>0.19843943205560055</v>
       </c>
-      <c r="G92" s="173">
+      <c r="G101" s="173">
         <f>Statement!Q205</f>
         <v>0.22095919166044045</v>
       </c>
-      <c r="I92" s="195"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B93" s="20" t="str">
+      <c r="I101" s="195"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B102" s="20" t="str">
         <f>Statement!B206</f>
         <v>Subscription services</v>
       </c>
-      <c r="C93" s="173">
+      <c r="C102" s="173">
         <f>Statement!M206</f>
         <v>1</v>
       </c>
-      <c r="D93" s="173">
+      <c r="D102" s="173">
         <f>Statement!N206</f>
         <v>0.10859984890455805</v>
       </c>
-      <c r="E93" s="173">
+      <c r="E102" s="173">
         <f>Statement!O206</f>
         <v>0.14171730365154184</v>
       </c>
-      <c r="F93" s="173">
+      <c r="F102" s="173">
         <f>Statement!P206</f>
         <v>0.10358377477679126</v>
       </c>
-      <c r="G93" s="173">
+      <c r="G102" s="173">
         <f>Statement!Q206</f>
         <v>0.11819984675711002</v>
       </c>
-      <c r="I93" s="195"/>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B94" s="20" t="str">
+      <c r="I102" s="195"/>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B103" s="20" t="str">
         <f>Statement!B207</f>
         <v>Other</v>
       </c>
-      <c r="C94" s="173">
+      <c r="C103" s="173">
         <f>Statement!M207</f>
         <v>1</v>
       </c>
-      <c r="D94" s="173">
+      <c r="D103" s="173">
         <f>Statement!N207</f>
         <v>0.9517463235294118</v>
       </c>
-      <c r="E94" s="173">
+      <c r="E103" s="173">
         <f>Statement!O207</f>
         <v>0.16741229102896163</v>
       </c>
-      <c r="F94" s="173">
+      <c r="F103" s="173">
         <f>Statement!P207</f>
         <v>9.419120613150464E-2</v>
       </c>
-      <c r="G94" s="173">
+      <c r="G103" s="173">
         <f>Statement!Q207</f>
         <v>9.4009216589861749E-2</v>
       </c>
-      <c r="I94" s="195"/>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B95" s="20" t="str">
+      <c r="I103" s="195"/>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B104" s="20" t="str">
         <f>Statement!B208</f>
         <v>Retail</v>
       </c>
-      <c r="C95" s="173">
+      <c r="C104" s="173">
         <f>Statement!M208</f>
         <v>1</v>
       </c>
-      <c r="D95" s="173">
+      <c r="D104" s="173">
         <f>Statement!N208</f>
         <v>6.4439919532898293E-2</v>
       </c>
-      <c r="E95" s="173">
+      <c r="E104" s="173">
         <f>Statement!O208</f>
         <v>0.11556234687833468</v>
       </c>
-      <c r="F95" s="173">
+      <c r="F104" s="173">
         <f>Statement!P208</f>
         <v>9.5810572942061203E-2</v>
       </c>
-      <c r="G95" s="173">
+      <c r="G104" s="173">
         <f>Statement!Q208</f>
         <v>0.108966201171562</v>
       </c>
-      <c r="I95" s="195"/>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B96" s="20" t="str">
+      <c r="I104" s="195"/>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B105" s="20" t="str">
         <f>Statement!B209</f>
         <v>AWS</v>
       </c>
-      <c r="C96" s="173">
+      <c r="C105" s="173">
         <f>Statement!M209</f>
         <v>1</v>
       </c>
-      <c r="D96" s="173">
+      <c r="D105" s="173">
         <f>Statement!N209</f>
         <v>0.28767563743931063</v>
       </c>
-      <c r="E96" s="173">
+      <c r="E105" s="173">
         <f>Statement!O209</f>
         <v>0.13310277666799841</v>
       </c>
-      <c r="F96" s="173">
+      <c r="F105" s="173">
         <f>Statement!P209</f>
         <v>0.18509867007503553</v>
       </c>
-      <c r="G96" s="173">
+      <c r="G105" s="173">
         <f>Statement!Q209</f>
         <v>0.19681840157685299</v>
       </c>
-      <c r="I96" s="195"/>
-    </row>
-    <row r="98" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
-      <c r="I98" s="14"/>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B99" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="C99" s="173">
-        <f>Statement!M216</f>
-        <v>0</v>
-      </c>
-      <c r="D99" s="173">
-        <f>Statement!N216</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="173">
-        <f>Statement!O216</f>
-        <v>0</v>
-      </c>
-      <c r="F99" s="173">
-        <f>Statement!P216</f>
-        <v>0</v>
-      </c>
-      <c r="G99" s="173">
-        <f>Statement!Q216</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="195"/>
+      <c r="I105" s="195"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40645,14 +40827,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="256" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="255"/>
-      <c r="F3" s="256" t="s">
+      <c r="D3" s="257"/>
+      <c r="F3" s="258" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="255"/>
+      <c r="G3" s="257"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40719,19 +40901,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="252">
+      <c r="C7" s="254">
         <f>Statement!AA90</f>
         <v>0.10515152683741096</v>
       </c>
-      <c r="D7" s="253"/>
-      <c r="F7" s="252">
+      <c r="D7" s="255"/>
+      <c r="F7" s="254">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.19620517346245125</v>
       </c>
-      <c r="G7" s="253"/>
+      <c r="G7" s="255"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -40758,19 +40940,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="252">
+      <c r="C9" s="254">
         <f>Statement!AA91</f>
         <v>9.2887269938650305E-2</v>
       </c>
-      <c r="D9" s="253"/>
-      <c r="F9" s="252">
+      <c r="D9" s="255"/>
+      <c r="F9" s="254">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17442524699161868</v>
       </c>
-      <c r="G9" s="253"/>
+      <c r="G9" s="255"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -40797,19 +40979,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="252">
+      <c r="C11" s="254">
         <f>Statement!AA92</f>
         <v>0.12623002381415968</v>
       </c>
-      <c r="D11" s="253"/>
-      <c r="F11" s="252">
+      <c r="D11" s="255"/>
+      <c r="F11" s="254">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.2343844903721457</v>
       </c>
-      <c r="G11" s="253"/>
+      <c r="G11" s="255"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -40836,19 +41018,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="252">
+      <c r="C13" s="254">
         <f>Statement!AA96</f>
         <v>0.11229173948502855</v>
       </c>
-      <c r="D13" s="253"/>
-      <c r="F13" s="252">
+      <c r="D13" s="255"/>
+      <c r="F13" s="254">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.14343889234896756</v>
       </c>
-      <c r="G13" s="253"/>
+      <c r="G13" s="255"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -40875,19 +41057,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="252">
+      <c r="C15" s="254">
         <f>Statement!AA97</f>
         <v>0.1513080664095254</v>
       </c>
-      <c r="D15" s="253"/>
-      <c r="F15" s="252">
+      <c r="D15" s="255"/>
+      <c r="F15" s="254">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.43242397371029156</v>
       </c>
-      <c r="G15" s="253"/>
+      <c r="G15" s="255"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -40914,19 +41096,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="252">
+      <c r="C17" s="254">
         <f>Statement!AA99</f>
         <v>-0.32163775310983433</v>
       </c>
-      <c r="D17" s="253"/>
-      <c r="F17" s="252">
+      <c r="D17" s="255"/>
+      <c r="F17" s="254">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.33048887910151947</v>
       </c>
-      <c r="G17" s="253"/>
+      <c r="G17" s="255"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -40953,22 +41135,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="252">
+      <c r="C19" s="254">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>2.6669118999448223E-3</v>
       </c>
-      <c r="D19" s="253"/>
-      <c r="F19" s="252">
+      <c r="D19" s="255"/>
+      <c r="F19" s="254">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>8.976494540070332E-3</v>
       </c>
-      <c r="G19" s="253"/>
+      <c r="G19" s="255"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -40995,22 +41177,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="252">
+      <c r="C21" s="254">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.3234420734950324</v>
       </c>
-      <c r="D21" s="253"/>
-      <c r="F21" s="252">
+      <c r="D21" s="255"/>
+      <c r="F21" s="254">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.33608268584880524</v>
       </c>
-      <c r="G21" s="253"/>
+      <c r="G21" s="255"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -41059,22 +41241,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="252">
+      <c r="C25" s="254">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>9.6149656052541471E-2</v>
       </c>
-      <c r="D25" s="253"/>
-      <c r="F25" s="252">
+      <c r="D25" s="255"/>
+      <c r="F25" s="254">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.14551516630072375</v>
       </c>
-      <c r="G25" s="253"/>
+      <c r="G25" s="255"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -41102,22 +41284,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="252">
+      <c r="C27" s="254">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>1.5557476231633535E-3</v>
       </c>
-      <c r="D27" s="253"/>
-      <c r="F27" s="252">
+      <c r="D27" s="255"/>
+      <c r="F27" s="254">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>3.5567470956210906E-2</v>
       </c>
-      <c r="G27" s="253"/>
+      <c r="G27" s="255"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -41145,22 +41327,22 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="252">
+      <c r="C29" s="254">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.12511424310933666</v>
       </c>
-      <c r="D29" s="253"/>
-      <c r="F29" s="252">
+      <c r="D29" s="255"/>
+      <c r="F29" s="254">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.15941310597799146</v>
       </c>
-      <c r="G29" s="253"/>
+      <c r="G29" s="255"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="str">
@@ -41188,22 +41370,22 @@
       <c r="B31" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C31" s="252">
+      <c r="C31" s="254">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.14881401148292062</v>
       </c>
-      <c r="D31" s="253"/>
-      <c r="F31" s="252">
+      <c r="D31" s="255"/>
+      <c r="F31" s="254">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.26220211545813688</v>
       </c>
-      <c r="G31" s="253"/>
+      <c r="G31" s="255"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="str">
@@ -41231,22 +41413,22 @@
       <c r="B33" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C33" s="252">
+      <c r="C33" s="254">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.2566470544425413E-2</v>
       </c>
-      <c r="D33" s="253"/>
-      <c r="F33" s="252">
+      <c r="D33" s="255"/>
+      <c r="F33" s="254">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12467234600262123</v>
       </c>
-      <c r="G33" s="253"/>
+      <c r="G33" s="255"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="str">
@@ -41274,22 +41456,22 @@
       <c r="B35" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C35" s="252">
+      <c r="C35" s="254">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>0.11185410334346504</v>
       </c>
-      <c r="D35" s="253"/>
-      <c r="F35" s="252">
+      <c r="D35" s="255"/>
+      <c r="F35" s="254">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.2201467645096731</v>
       </c>
-      <c r="G35" s="253"/>
+      <c r="G35" s="255"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="32" t="str">
@@ -41318,23 +41500,23 @@
       <c r="B37" s="247" t="s">
         <v>316</v>
       </c>
-      <c r="C37" s="257">
+      <c r="C37" s="252">
         <f>IF(C36=0,
 IF(D36=0,0,IF(D36&gt;0,1,-1)),
 (D36-C36)/ABS(C36)
 )</f>
         <v>0.10033904899535892</v>
       </c>
-      <c r="D37" s="258"/>
+      <c r="D37" s="253"/>
       <c r="E37" s="16"/>
-      <c r="F37" s="257">
+      <c r="F37" s="252">
         <f>IF(F36=0,
 IF(G36=0,0,IF(G36&gt;0,1,-1)),
 (G36-F36)/ABS(F36)
 )</f>
         <v>0.15745931052627732</v>
       </c>
-      <c r="G37" s="258"/>
+      <c r="G37" s="253"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="32" t="str">
@@ -41363,26 +41545,50 @@
       <c r="B39" s="247" t="s">
         <v>316</v>
       </c>
-      <c r="C39" s="257">
+      <c r="C39" s="252">
         <f>IF(C38=0,
 IF(D38=0,0,IF(D38&gt;0,1,-1)),
 (D38-C38)/ABS(C38)
 )</f>
         <v>0.12357996115678294</v>
       </c>
-      <c r="D39" s="258"/>
+      <c r="D39" s="253"/>
       <c r="E39" s="16"/>
-      <c r="F39" s="257">
+      <c r="F39" s="252">
         <f>IF(F38=0,
 IF(G38=0,0,IF(G38&gt;0,1,-1)),
 (G38-F38)/ABS(F38)
 )</f>
         <v>0.36952362421766061</v>
       </c>
-      <c r="G39" s="258"/>
+      <c r="G39" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="C39:D39"/>
@@ -41393,30 +41599,6 @@
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="F35:G35"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
